--- a/artfynd/A 27558-2024 artfynd.xlsx
+++ b/artfynd/A 27558-2024 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>121066999</v>
       </c>
       <c r="B5" t="n">
-        <v>78334</v>
+        <v>78337</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 27558-2024 artfynd.xlsx
+++ b/artfynd/A 27558-2024 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>121066999</v>
       </c>
       <c r="B5" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 27558-2024 artfynd.xlsx
+++ b/artfynd/A 27558-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112381903</v>
+        <v>120656259</v>
       </c>
       <c r="B2" t="n">
-        <v>55724</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kråkhemshobben, Storuman, Ly lm</t>
+          <t>Kråkhemsmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606379</v>
+        <v>606245</v>
       </c>
       <c r="R2" t="n">
         <v>7222710</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,35 +760,30 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>Ecogain</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120656259</v>
+        <v>121067001</v>
       </c>
       <c r="B3" t="n">
-        <v>78594</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,14 +807,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kråkhemsmyran, Ly lm</t>
+          <t>Rackolidem, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606245</v>
+        <v>606354</v>
       </c>
       <c r="R3" t="n">
-        <v>7222710</v>
+        <v>7222798</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,12 +861,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,50 +877,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120656260</v>
+        <v>121066999</v>
       </c>
       <c r="B4" t="n">
-        <v>97973</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kråkhemsmyran, Ly lm</t>
+          <t>Rackolidem, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606243</v>
+        <v>606203</v>
       </c>
       <c r="R4" t="n">
-        <v>7222707</v>
+        <v>7222715</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,12 +962,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,50 +978,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121066999</v>
+        <v>112381903</v>
       </c>
       <c r="B5" t="n">
-        <v>78340</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rackolidem, Ly lm</t>
+          <t>Kråkhemshobben, Storuman, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606203</v>
+        <v>606378</v>
       </c>
       <c r="R5" t="n">
-        <v>7222715</v>
+        <v>7222710</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,15 +1063,217 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120656260</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kråkhemsmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>606243</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7222707</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121066998</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rackolidem, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>606162</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7222715</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 27558-2024 artfynd.xlsx
+++ b/artfynd/A 27558-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120656259</v>
+        <v>135339378</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>79452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kråkhemsmyran, Ly lm</t>
+          <t>Kråkhemshobben, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606245</v>
+        <v>606431</v>
       </c>
       <c r="R2" t="n">
-        <v>7222710</v>
+        <v>7222651</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,23 +770,23 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Ecogain</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121067001</v>
+        <v>120656259</v>
       </c>
       <c r="B3" t="n">
         <v>79327</v>
@@ -807,14 +817,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rackolidem, Ly lm</t>
+          <t>Kråkhemsmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606354</v>
+        <v>606245</v>
       </c>
       <c r="R3" t="n">
-        <v>7222798</v>
+        <v>7222710</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -841,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,12 +871,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -877,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121066999</v>
+        <v>121067001</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606203</v>
+        <v>606354</v>
       </c>
       <c r="R4" t="n">
-        <v>7222715</v>
+        <v>7222798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,48 +988,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112381903</v>
+        <v>135339371</v>
       </c>
       <c r="B5" t="n">
-        <v>57132</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kråkhemshobben, Storuman, Ly lm</t>
+          <t>Kråkhemshobben, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606378</v>
+        <v>606207</v>
       </c>
       <c r="R5" t="n">
-        <v>7222710</v>
+        <v>7222530</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1043,12 +1053,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,64 +1083,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120656260</v>
+        <v>135339375</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kråkhemsmyran, Ly lm</t>
+          <t>Kråkhemshobben, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606243</v>
+        <v>606378</v>
       </c>
       <c r="R6" t="n">
-        <v>7222707</v>
+        <v>7222624</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1144,12 +1164,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1164,64 +1194,64 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Ecogain</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121066998</v>
+        <v>135339386</v>
       </c>
       <c r="B7" t="n">
-        <v>79085</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rackolidem, Ly lm</t>
+          <t>Kråkhemshobben, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606162</v>
+        <v>606490</v>
       </c>
       <c r="R7" t="n">
-        <v>7222715</v>
+        <v>7222604</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,12 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,17 +1305,2193 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135339391</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>606377</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7222769</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135339396</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>606242</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7222625</v>
+      </c>
+      <c r="S9" t="n">
+        <v>33</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gott om i granstråk</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121066999</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rackolidem, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>606203</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7222715</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135339394</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>606286</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7222634</v>
+      </c>
+      <c r="S11" t="n">
+        <v>12</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135339392</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>606368</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7222745</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135339369</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>606147</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7222547</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135339377</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>606423</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7222643</v>
+      </c>
+      <c r="S14" t="n">
+        <v>14</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påbörjade ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135339379</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>606439</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7222635</v>
+      </c>
+      <c r="S15" t="n">
+        <v>14</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påbörjade ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135339380</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>606436</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7222635</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påbörjade ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135339381</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>606457</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7222627</v>
+      </c>
+      <c r="S17" t="n">
+        <v>14</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135339383</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>606478</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7222605</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135339385</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>606484</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7222604</v>
+      </c>
+      <c r="S19" t="n">
+        <v>13</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påbörjade ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135339370</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>606193</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7222575</v>
+      </c>
+      <c r="S20" t="n">
+        <v>17</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135339382</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>606471</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7222629</v>
+      </c>
+      <c r="S21" t="n">
+        <v>14</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>112381903</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>606378</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7222710</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120656260</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kråkhemsmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>606243</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7222707</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121066998</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rackolidem, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>606162</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7222715</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135339376</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>606376</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7222630</v>
+      </c>
+      <c r="S25" t="n">
+        <v>22</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135339390</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>606415</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7222774</v>
+      </c>
+      <c r="S26" t="n">
+        <v>9</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 27558-2024 artfynd.xlsx
+++ b/artfynd/A 27558-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120656259</v>
+        <v>135339378</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kråkhemsmyran, Ly lm</t>
+          <t>Kråkhemshobben, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606245</v>
+        <v>606431</v>
       </c>
       <c r="R2" t="n">
-        <v>7222710</v>
+        <v>7222651</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,28 +775,28 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Ecogain</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120656259</t>
+          <t>https://artportalen.se/Sighting/135339378</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121067001</v>
+        <v>120656259</v>
       </c>
       <c r="B3" t="n">
         <v>79327</v>
@@ -817,14 +827,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rackolidem, Ly lm</t>
+          <t>Kråkhemsmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606354</v>
+        <v>606245</v>
       </c>
       <c r="R3" t="n">
-        <v>7222798</v>
+        <v>7222710</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,12 +881,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -886,38 +896,38 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121067001</t>
+          <t>https://artportalen.se/Sighting/120656259</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121066999</v>
+        <v>121067001</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606203</v>
+        <v>606354</v>
       </c>
       <c r="R4" t="n">
-        <v>7222715</v>
+        <v>7222798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,54 +1002,54 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121066999</t>
+          <t>https://artportalen.se/Sighting/121067001</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112381903</v>
+        <v>135339371</v>
       </c>
       <c r="B5" t="n">
-        <v>57132</v>
+        <v>79441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kråkhemshobben, Storuman, Ly lm</t>
+          <t>Kråkhemshobben, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>606378</v>
+        <v>606207</v>
       </c>
       <c r="R5" t="n">
-        <v>7222710</v>
+        <v>7222530</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,12 +1073,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,69 +1103,69 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112381903</t>
+          <t>https://artportalen.se/Sighting/135339371</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120656260</v>
+        <v>135339375</v>
       </c>
       <c r="B6" t="n">
-        <v>99035</v>
+        <v>79441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kråkhemsmyran, Ly lm</t>
+          <t>Kråkhemshobben, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>606243</v>
+        <v>606378</v>
       </c>
       <c r="R6" t="n">
-        <v>7222707</v>
+        <v>7222624</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1169,12 +1189,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-06-18</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,69 +1219,69 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Ecogain</t>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120656260</t>
+          <t>https://artportalen.se/Sighting/135339375</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121066998</v>
+        <v>135339386</v>
       </c>
       <c r="B7" t="n">
-        <v>79085</v>
+        <v>79441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rackolidem, Ly lm</t>
+          <t>Kråkhemshobben, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>606162</v>
+        <v>606490</v>
       </c>
       <c r="R7" t="n">
-        <v>7222715</v>
+        <v>7222604</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1275,12 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,22 +1335,2293 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339386</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135339391</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>606377</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7222769</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339391</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135339396</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>606242</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7222625</v>
+      </c>
+      <c r="S9" t="n">
+        <v>33</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gott om i granstråk</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339396</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121066999</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rackolidem, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>606203</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7222715</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
+      <c r="AY10" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121066999</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135339394</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79198</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>606286</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7222634</v>
+      </c>
+      <c r="S11" t="n">
+        <v>12</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339394</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135339392</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>606368</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7222745</v>
+      </c>
+      <c r="S12" t="n">
+        <v>14</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:33</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339392</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135339369</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>606147</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7222547</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Skalad gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339369</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135339377</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>606423</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7222643</v>
+      </c>
+      <c r="S14" t="n">
+        <v>14</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påbörjade ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339377</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135339379</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>606439</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7222635</v>
+      </c>
+      <c r="S15" t="n">
+        <v>14</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påbörjade ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339379</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135339380</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>606436</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7222635</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påbörjade ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339380</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135339381</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>606457</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7222627</v>
+      </c>
+      <c r="S17" t="n">
+        <v>14</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339381</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135339383</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>606478</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7222605</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack tall</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339383</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135339385</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>606484</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7222604</v>
+      </c>
+      <c r="S19" t="n">
+        <v>13</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påbörjade ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339385</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135339370</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>606193</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7222575</v>
+      </c>
+      <c r="S20" t="n">
+        <v>17</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339370</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135339382</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>606471</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7222629</v>
+      </c>
+      <c r="S21" t="n">
+        <v>14</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339382</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>112381903</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>606378</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7222710</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112381903</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120656260</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kråkhemsmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>606243</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7222707</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120656260</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121066998</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Rackolidem, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>606162</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7222715</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/121066998</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135339376</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>606376</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7222630</v>
+      </c>
+      <c r="S25" t="n">
+        <v>22</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:56</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339376</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135339390</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kråkhemshobben, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>606415</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7222774</v>
+      </c>
+      <c r="S26" t="n">
+        <v>9</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135339390</t>
         </is>
       </c>
     </row>
@@ -1322,6 +3633,25 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
